--- a/selenium_model/APPIUM_END_TO_END_300_REPORT.xlsx
+++ b/selenium_model/APPIUM_END_TO_END_300_REPORT.xlsx
@@ -858,7 +858,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G265" t="n">
